--- a/output2.xlsx
+++ b/output2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AZM\Desktop\electronic-component-price-scraper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1B58FC-BC35-4D11-AF32-E63C45678B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877E2303-A460-4F75-AE01-9700B248203C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -204,7 +204,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,12 +297,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -321,7 +315,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -340,7 +334,6 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -704,7 +697,7 @@
       <c r="F3" s="3">
         <v>2601536</v>
       </c>
-      <c r="G3" s="18"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C4" s="4" t="s">
@@ -719,7 +712,7 @@
       <c r="F4" s="3">
         <v>6528000</v>
       </c>
-      <c r="G4" s="18"/>
+      <c r="G4" s="17"/>
     </row>
     <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -740,7 +733,7 @@
       <c r="F5" s="3">
         <v>28368</v>
       </c>
-      <c r="G5" s="18"/>
+      <c r="G5" s="17"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -782,7 +775,7 @@
       <c r="F7" s="3">
         <v>11800000</v>
       </c>
-      <c r="G7" s="18"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -803,7 +796,7 @@
       <c r="F8" s="3">
         <v>7560000</v>
       </c>
-      <c r="G8" s="18"/>
+      <c r="G8" s="17"/>
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -866,7 +859,7 @@
       <c r="F11" s="3">
         <v>6204000</v>
       </c>
-      <c r="G11" s="18"/>
+      <c r="G11" s="17"/>
     </row>
     <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -887,7 +880,7 @@
       <c r="F12" s="3">
         <v>13624000</v>
       </c>
-      <c r="G12" s="18"/>
+      <c r="G12" s="17"/>
     </row>
     <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -908,7 +901,7 @@
       <c r="F13" s="3">
         <v>750000</v>
       </c>
-      <c r="G13" s="18"/>
+      <c r="G13" s="17"/>
     </row>
     <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -929,7 +922,7 @@
       <c r="F14" s="3">
         <v>480000</v>
       </c>
-      <c r="G14" s="18"/>
+      <c r="G14" s="17"/>
     </row>
     <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -950,7 +943,7 @@
       <c r="F15" s="3">
         <v>28675000</v>
       </c>
-      <c r="G15" s="18"/>
+      <c r="G15" s="17"/>
     </row>
     <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -992,7 +985,7 @@
       <c r="F17" s="3">
         <v>3170000</v>
       </c>
-      <c r="G17" s="18"/>
+      <c r="G17" s="17"/>
     </row>
     <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18">
@@ -1013,7 +1006,7 @@
       <c r="F18" s="3">
         <v>1439000</v>
       </c>
-      <c r="G18" s="18"/>
+      <c r="G18" s="17"/>
     </row>
     <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19">
@@ -1034,7 +1027,7 @@
       <c r="F19" s="3">
         <v>840000</v>
       </c>
-      <c r="G19" s="18"/>
+      <c r="G19" s="17"/>
     </row>
     <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20">
@@ -1076,7 +1069,7 @@
       <c r="F21" s="3">
         <v>28805000</v>
       </c>
-      <c r="G21" s="18"/>
+      <c r="G21" s="17"/>
     </row>
     <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22">
@@ -1097,7 +1090,7 @@
       <c r="F22" s="3">
         <v>1290000</v>
       </c>
-      <c r="G22" s="18"/>
+      <c r="G22" s="17"/>
     </row>
     <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23">
@@ -1118,7 +1111,7 @@
       <c r="F23" s="3">
         <v>1060000</v>
       </c>
-      <c r="G23" s="18"/>
+      <c r="G23" s="17"/>
     </row>
     <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24">
@@ -1139,7 +1132,7 @@
       <c r="F24" s="3">
         <v>4000000</v>
       </c>
-      <c r="G24" s="18"/>
+      <c r="G24" s="17"/>
     </row>
     <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25">
@@ -1160,7 +1153,7 @@
       <c r="F25" s="3">
         <v>350000</v>
       </c>
-      <c r="G25" s="18"/>
+      <c r="G25" s="17"/>
     </row>
     <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26">
@@ -1202,7 +1195,7 @@
       <c r="F27" s="3">
         <v>144000</v>
       </c>
-      <c r="G27" s="18"/>
+      <c r="G27" s="17"/>
     </row>
     <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28">
@@ -1244,7 +1237,7 @@
       <c r="F29" s="3">
         <v>6122</v>
       </c>
-      <c r="G29" s="18"/>
+      <c r="G29" s="17"/>
     </row>
     <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30">
@@ -1370,7 +1363,7 @@
       <c r="F35" s="3">
         <v>8619843</v>
       </c>
-      <c r="G35" s="18"/>
+      <c r="G35" s="17"/>
     </row>
     <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36">
@@ -1454,7 +1447,7 @@
       <c r="F39" s="3">
         <v>600000</v>
       </c>
-      <c r="G39" s="18"/>
+      <c r="G39" s="17"/>
     </row>
     <row r="40" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40">
@@ -1517,7 +1510,7 @@
       <c r="F42" s="3">
         <v>15000</v>
       </c>
-      <c r="G42" s="18"/>
+      <c r="G42" s="17"/>
     </row>
     <row r="43" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43">
@@ -1538,7 +1531,7 @@
       <c r="F43" s="3">
         <v>11477000</v>
       </c>
-      <c r="G43" s="18"/>
+      <c r="G43" s="17"/>
     </row>
     <row r="44" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44">
@@ -1601,7 +1594,7 @@
       <c r="F46" s="3">
         <v>6750000</v>
       </c>
-      <c r="G46" s="18"/>
+      <c r="G46" s="17"/>
     </row>
     <row r="47" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47">
@@ -1622,7 +1615,7 @@
       <c r="F47" s="3">
         <v>550000</v>
       </c>
-      <c r="G47" s="18"/>
+      <c r="G47" s="17"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E48" s="3" t="s">
